--- a/data/Diessenhofen/investment_decision/Diessenhofen_MFH_2005-2014_investment_decision.xlsx
+++ b/data/Diessenhofen/investment_decision/Diessenhofen_MFH_2005-2014_investment_decision.xlsx
@@ -470,22 +470,22 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>111.6665845633376</v>
+        <v>49.9400241098098</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -508,19 +508,19 @@
         <v>33543.23593815086</v>
       </c>
       <c r="F2" t="n">
-        <v>112.796555763525</v>
+        <v>46.4342901086579</v>
       </c>
       <c r="G2" t="n">
         <v>33543.23593815086</v>
       </c>
       <c r="H2" t="n">
-        <v>126.9431941078416</v>
+        <v>35.36801185262399</v>
       </c>
       <c r="I2" t="n">
         <v>33543.23593815086</v>
       </c>
       <c r="J2" t="n">
-        <v>126.9431941078416</v>
+        <v>37.18471638792212</v>
       </c>
       <c r="K2" t="n">
         <v>33543.23593815086</v>
@@ -531,7 +531,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>148.8137416286408</v>
+        <v>49.9400241098098</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -545,19 +545,19 @@
         <v>33543.23593815086</v>
       </c>
       <c r="F3" t="n">
-        <v>148.8401134935372</v>
+        <v>50.86174802343547</v>
       </c>
       <c r="G3" t="n">
         <v>33543.23593815086</v>
       </c>
       <c r="H3" t="n">
-        <v>156.1748799008996</v>
+        <v>49.61938609452334</v>
       </c>
       <c r="I3" t="n">
         <v>33543.23593815086</v>
       </c>
       <c r="J3" t="n">
-        <v>156.1748799008995</v>
+        <v>56.46557966129716</v>
       </c>
       <c r="K3" t="n">
         <v>33543.23593815086</v>
@@ -568,7 +568,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>171.3321455604864</v>
+        <v>152.5052156140532</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,19 +582,19 @@
         <v>33543.23593815086</v>
       </c>
       <c r="F4" t="n">
-        <v>170.9340884896532</v>
+        <v>160.2892896369156</v>
       </c>
       <c r="G4" t="n">
         <v>33543.23593815086</v>
       </c>
       <c r="H4" t="n">
-        <v>177.1993865878416</v>
+        <v>147.961731668349</v>
       </c>
       <c r="I4" t="n">
         <v>33543.23593815086</v>
       </c>
       <c r="J4" t="n">
-        <v>177.2349471854255</v>
+        <v>147.9842786890504</v>
       </c>
       <c r="K4" t="n">
         <v>33543.23593815086</v>
@@ -605,7 +605,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>181.0079130184467</v>
+        <v>152.5052156140532</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -619,19 +619,19 @@
         <v>33543.23593815086</v>
       </c>
       <c r="F5" t="n">
-        <v>181.0323608910093</v>
+        <v>160.2892896369156</v>
       </c>
       <c r="G5" t="n">
         <v>33543.23593815086</v>
       </c>
       <c r="H5" t="n">
-        <v>186.5033158094853</v>
+        <v>148.1805190934473</v>
       </c>
       <c r="I5" t="n">
         <v>33543.23593815086</v>
       </c>
       <c r="J5" t="n">
-        <v>185.8506236372445</v>
+        <v>147.9842786890504</v>
       </c>
       <c r="K5" t="n">
         <v>33543.23593815086</v>
@@ -642,7 +642,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>185.8529759700493</v>
+        <v>152.5052156140532</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -656,19 +656,19 @@
         <v>33543.23593815086</v>
       </c>
       <c r="F6" t="n">
-        <v>185.8529759700493</v>
+        <v>160.2892896369156</v>
       </c>
       <c r="G6" t="n">
         <v>33543.23593815086</v>
       </c>
       <c r="H6" t="n">
-        <v>190.4167674089326</v>
+        <v>148.1805190934473</v>
       </c>
       <c r="I6" t="n">
         <v>33543.23593815086</v>
       </c>
       <c r="J6" t="n">
-        <v>191.4271580801865</v>
+        <v>147.9842786890504</v>
       </c>
       <c r="K6" t="n">
         <v>33543.23593815086</v>
@@ -683,32 +683,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Diessenhofen_b_MFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Diessenhofen_b_MFH_2005-2014</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>50.31485390722629</v>
+        <v>101.804625</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>50.31485390722629</v>
+        <v>101.804625</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>29.37895859964304</v>
+        <v>59.44395403874213</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>29.37895859964304</v>
+        <v>59.44395403874213</v>
       </c>
     </row>
     <row r="8">
@@ -720,32 +720,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Diessenhofen_b_MFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Diessenhofen_b_MFH_2005-2014</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>50.31485390722629</v>
+        <v>101.804625</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>50.31485390722629</v>
+        <v>101.804625</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>38.99368060522514</v>
+        <v>78.89791429593279</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>38.99368060522514</v>
+        <v>78.89791429593279</v>
       </c>
     </row>
     <row r="9">
@@ -757,32 +757,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Diessenhofen_b_MFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Diessenhofen_b_MFH_2005-2014</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>50.31485390722629</v>
+        <v>101.804625</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>50.31485390722629</v>
+        <v>101.804625</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>43.19229981645839</v>
+        <v>87.39319592997143</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>43.19229981645839</v>
+        <v>87.39319592997143</v>
       </c>
     </row>
     <row r="10">
@@ -794,32 +794,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Diessenhofen_b_MFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Diessenhofen_b_MFH_2005-2014</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>50.31485390722629</v>
+        <v>101.804625</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>50.31485390722629</v>
+        <v>101.804625</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>45.37458906675955</v>
+        <v>91.80873371883369</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>45.37458906675955</v>
+        <v>91.80873371883369</v>
       </c>
     </row>
     <row r="11">
@@ -831,32 +831,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Diessenhofen_b_MFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Diessenhofen_b_MFH_2005-2014</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>50.31485390722629</v>
+        <v>101.804625</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>50.31485390722629</v>
+        <v>101.804625</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>46.64710201727575</v>
+        <v>94.38347444994686</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>46.64710201727575</v>
+        <v>94.38347444994686</v>
       </c>
     </row>
     <row r="12">
@@ -864,7 +864,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.01699841804470588</v>
+        <v>0.01466628782577868</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -878,19 +878,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01718465927839513</v>
+        <v>0.01478123308235294</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.01773747969882353</v>
+        <v>0.0140421714282353</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.01773747969882353</v>
+        <v>0.0140421714282353</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -901,7 +901,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.01699841804470588</v>
+        <v>0.01466628782577868</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -915,19 +915,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01718465927839513</v>
+        <v>0.01478123308235294</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.01773747969882353</v>
+        <v>0.0140421714282353</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.01773747969882353</v>
+        <v>0.0140421714282353</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -938,7 +938,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.01699841804470588</v>
+        <v>0.01466628782577868</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -952,19 +952,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01718465927839513</v>
+        <v>0.01478123308235294</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.01773747969882353</v>
+        <v>0.0140421714282353</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01773747969882353</v>
+        <v>0.0140421714282353</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -975,7 +975,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.018410986211039</v>
+        <v>0.01466628782577868</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -989,19 +989,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01843698115169093</v>
+        <v>0.01478123308235294</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.01858330046354267</v>
+        <v>0.0140421714282353</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.01863871145149551</v>
+        <v>0.0140421714282353</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1012,7 +1012,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.018410986211039</v>
+        <v>0.01466628782577868</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1026,19 +1026,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.01843698115169093</v>
+        <v>0.01478123308235294</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01858330046354267</v>
+        <v>0.0140421714282353</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01863871145149551</v>
+        <v>0.0140421714282353</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1049,7 +1049,7 @@
         <v>46023</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4739409428155806</v>
+        <v>0.9140726301101088</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1063,19 +1063,19 @@
         <v>2.6384501052</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4690217674629834</v>
+        <v>0.9221874955254233</v>
       </c>
       <c r="G17" t="n">
         <v>2.6384501052</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3529701486721672</v>
+        <v>0.7179451027583194</v>
       </c>
       <c r="I17" t="n">
         <v>2.6384501052</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3529701486721672</v>
+        <v>0.7100276955079132</v>
       </c>
       <c r="K17" t="n">
         <v>2.6384501052</v>
@@ -1086,7 +1086,7 @@
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.4739409428155806</v>
+        <v>0.9140726301101088</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1100,19 +1100,19 @@
         <v>2.6384501052</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4690217674629834</v>
+        <v>0.9221874955254233</v>
       </c>
       <c r="G18" t="n">
         <v>2.6384501052</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3529701486721672</v>
+        <v>0.7179451027583194</v>
       </c>
       <c r="I18" t="n">
         <v>2.6384501052</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3529701486721671</v>
+        <v>0.7100276955079132</v>
       </c>
       <c r="K18" t="n">
         <v>2.6384501052</v>
@@ -1123,7 +1123,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.4739409428155806</v>
+        <v>0.9140726301101088</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1137,19 +1137,19 @@
         <v>2.6384501052</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4690217674629834</v>
+        <v>0.9221874955254233</v>
       </c>
       <c r="G19" t="n">
         <v>2.6384501052</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3529701486721672</v>
+        <v>0.7179451027583194</v>
       </c>
       <c r="I19" t="n">
         <v>2.6384501052</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3529701486721671</v>
+        <v>0.7100276955079132</v>
       </c>
       <c r="K19" t="n">
         <v>2.6384501052</v>
@@ -1160,7 +1160,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.1640158353271071</v>
+        <v>0.3650344265249042</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1174,19 +1174,19 @@
         <v>2.6384501052</v>
       </c>
       <c r="F20" t="n">
-        <v>0.161253872882839</v>
+        <v>0.3754873719338821</v>
       </c>
       <c r="G20" t="n">
         <v>2.6384501052</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1457074459985918</v>
+        <v>0.3452344395351535</v>
       </c>
       <c r="I20" t="n">
         <v>2.6384501052</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1398200285286026</v>
+        <v>0.3450537850007295</v>
       </c>
       <c r="K20" t="n">
         <v>2.6384501052</v>
@@ -1197,7 +1197,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.1640158353271071</v>
+        <v>0.3672548289178262</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1211,19 +1211,19 @@
         <v>2.6384501052</v>
       </c>
       <c r="F21" t="n">
-        <v>0.161253872882839</v>
+        <v>0.3754873719338821</v>
       </c>
       <c r="G21" t="n">
         <v>2.6384501052</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1457074459985918</v>
+        <v>0.3479647332794337</v>
       </c>
       <c r="I21" t="n">
         <v>2.6384501052</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1398200285286027</v>
+        <v>0.3450537850007295</v>
       </c>
       <c r="K21" t="n">
         <v>2.6384501052</v>
@@ -1419,7 +1419,7 @@
         <v>46023</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>0.09073823426101546</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1433,19 +1433,19 @@
         <v>2.6384501052</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>0.09073823426101546</v>
       </c>
       <c r="G27" t="n">
         <v>2.6384501052</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>0.2355759022500002</v>
       </c>
       <c r="I27" t="n">
         <v>2.6384501052</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.2355759022500002</v>
       </c>
       <c r="K27" t="n">
         <v>2.6384501052</v>
@@ -1456,7 +1456,7 @@
         <v>47849</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>0.2544431293756351</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1470,19 +1470,19 @@
         <v>2.6384501052</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.2435752400671363</v>
       </c>
       <c r="G28" t="n">
         <v>2.6384501052</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.4570249239337406</v>
       </c>
       <c r="I28" t="n">
         <v>2.6384501052</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.4569686560923318</v>
       </c>
       <c r="K28" t="n">
         <v>2.6384501052</v>
@@ -1493,7 +1493,7 @@
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.3282247225510279</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1507,19 +1507,19 @@
         <v>2.6384501052</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.3141012030000001</v>
       </c>
       <c r="G29" t="n">
         <v>2.6384501052</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.4570249239337406</v>
       </c>
       <c r="I29" t="n">
         <v>2.6384501052</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.4569686560923318</v>
       </c>
       <c r="K29" t="n">
         <v>2.6384501052</v>
@@ -1530,7 +1530,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.4298675389112773</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1544,19 +1544,19 @@
         <v>2.6384501052</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.4071546769162913</v>
       </c>
       <c r="G30" t="n">
         <v>2.6384501052</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.4564789229209824</v>
       </c>
       <c r="I30" t="n">
         <v>2.6384501052</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.4569686560923317</v>
       </c>
       <c r="K30" t="n">
         <v>2.6384501052</v>
@@ -1567,7 +1567,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.4594564041975866</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1581,19 +1581,19 @@
         <v>2.6384501052</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.4327024549235032</v>
       </c>
       <c r="G31" t="n">
         <v>2.6384501052</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.4919658494111916</v>
       </c>
       <c r="I31" t="n">
         <v>2.6384501052</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.492339529578796</v>
       </c>
       <c r="K31" t="n">
         <v>2.6384501052</v>
@@ -2142,13 +2142,13 @@
         <v>7.33469508502213</v>
       </c>
       <c r="H46" t="n">
-        <v>6.676743032915042</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>6.603465200218124</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>6.676743032915042</v>
       </c>
       <c r="K46" t="n">
         <v>6.603465200218124</v>
@@ -2344,7 +2344,7 @@
         <v>46023</v>
       </c>
       <c r="B52" t="n">
-        <v>1.370692394797091</v>
+        <v>1.378532473990305</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2358,19 +2358,19 @@
         <v>10.98945806195804</v>
       </c>
       <c r="F52" t="n">
-        <v>1.343660429347461</v>
+        <v>1.310551674818455</v>
       </c>
       <c r="G52" t="n">
         <v>10.98945806195804</v>
       </c>
       <c r="H52" t="n">
-        <v>1.283115183151797</v>
+        <v>1.222253339588949</v>
       </c>
       <c r="I52" t="n">
         <v>3.687502061258306</v>
       </c>
       <c r="J52" t="n">
-        <v>1.308214700093405</v>
+        <v>1.200014811060514</v>
       </c>
       <c r="K52" t="n">
         <v>3.687502061258306</v>
@@ -2381,7 +2381,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>1.941963167429007</v>
+        <v>2.043875345808601</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2395,19 +2395,19 @@
         <v>10.98945806195804</v>
       </c>
       <c r="F53" t="n">
-        <v>1.896874746021419</v>
+        <v>2.032592397398312</v>
       </c>
       <c r="G53" t="n">
         <v>10.98945806195804</v>
       </c>
       <c r="H53" t="n">
-        <v>1.880964489868401</v>
+        <v>2.047800319579351</v>
       </c>
       <c r="I53" t="n">
         <v>5.568352562268453</v>
       </c>
       <c r="J53" t="n">
-        <v>1.913422017634338</v>
+        <v>1.963995128373117</v>
       </c>
       <c r="K53" t="n">
         <v>5.568352562268453</v>
@@ -2418,7 +2418,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>2.217064312429164</v>
+        <v>2.361937933898064</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2432,19 +2432,19 @@
         <v>10.98945806195804</v>
       </c>
       <c r="F54" t="n">
-        <v>2.19495259054356</v>
+        <v>2.343528196827923</v>
       </c>
       <c r="G54" t="n">
         <v>10.98945806195804</v>
       </c>
       <c r="H54" t="n">
-        <v>2.184777953345784</v>
+        <v>2.383562447143415</v>
       </c>
       <c r="I54" t="n">
         <v>6.66132364501456</v>
       </c>
       <c r="J54" t="n">
-        <v>2.196375675422465</v>
+        <v>2.353757262210163</v>
       </c>
       <c r="K54" t="n">
         <v>6.66132364501456</v>
@@ -2455,7 +2455,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>2.171709152469975</v>
+        <v>2.273578217806827</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2469,19 +2469,19 @@
         <v>10.98945806195804</v>
       </c>
       <c r="F55" t="n">
-        <v>2.147616938662204</v>
+        <v>2.246946237756388</v>
       </c>
       <c r="G55" t="n">
         <v>10.98945806195804</v>
       </c>
       <c r="H55" t="n">
-        <v>2.13984372522008</v>
+        <v>2.198386828551805</v>
       </c>
       <c r="I55" t="n">
         <v>7.358667103005576</v>
       </c>
       <c r="J55" t="n">
-        <v>2.155989692054564</v>
+        <v>2.105298068352238</v>
       </c>
       <c r="K55" t="n">
         <v>7.358667103005576</v>
@@ -2492,7 +2492,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>2.148997919884338</v>
+        <v>2.268047697150078</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2506,19 +2506,19 @@
         <v>10.98945806195804</v>
       </c>
       <c r="F56" t="n">
-        <v>2.125020305479203</v>
+        <v>2.246946237756389</v>
       </c>
       <c r="G56" t="n">
         <v>10.98945806195804</v>
       </c>
       <c r="H56" t="n">
-        <v>2.12149942084767</v>
+        <v>2.198386828551808</v>
       </c>
       <c r="I56" t="n">
         <v>7.834241507947763</v>
       </c>
       <c r="J56" t="n">
-        <v>2.129849686853273</v>
+        <v>2.105146612603036</v>
       </c>
       <c r="K56" t="n">
         <v>7.834241507947763</v>
@@ -2788,7 +2788,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>1.591913298024732</v>
+        <v>0.3236531046116599</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2802,19 +2802,19 @@
         <v>10.98945806195804</v>
       </c>
       <c r="F64" t="n">
-        <v>1.615890912429866</v>
+        <v>0.2948332705644914</v>
       </c>
       <c r="G64" t="n">
         <v>10.98945806195804</v>
       </c>
       <c r="H64" t="n">
-        <v>1.596696964792383</v>
+        <v>0.3347877406632235</v>
       </c>
       <c r="I64" t="n">
         <v>10.98945806195804</v>
       </c>
       <c r="J64" t="n">
-        <v>1.584932552414528</v>
+        <v>0.3644592256260759</v>
       </c>
       <c r="K64" t="n">
         <v>10.98945806195804</v>
@@ -2825,7 +2825,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>1.591913298024732</v>
+        <v>0.4361112895385732</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2839,19 +2839,19 @@
         <v>10.98945806195804</v>
       </c>
       <c r="F65" t="n">
-        <v>1.615890912429866</v>
+        <v>0.4087076076879284</v>
       </c>
       <c r="G65" t="n">
         <v>10.98945806195804</v>
       </c>
       <c r="H65" t="n">
-        <v>1.598019024691633</v>
+        <v>0.5186659873028179</v>
       </c>
       <c r="I65" t="n">
         <v>10.98945806195804</v>
       </c>
       <c r="J65" t="n">
-        <v>1.584932552414528</v>
+        <v>0.6130698752332027</v>
       </c>
       <c r="K65" t="n">
         <v>10.98945806195804</v>
@@ -2862,7 +2862,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>1.591913298024732</v>
+        <v>0.4361112895385732</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2876,19 +2876,19 @@
         <v>10.98945806195804</v>
       </c>
       <c r="F66" t="n">
-        <v>1.615890912429866</v>
+        <v>0.4087076076879284</v>
       </c>
       <c r="G66" t="n">
         <v>10.98945806195804</v>
       </c>
       <c r="H66" t="n">
-        <v>1.598019024691633</v>
+        <v>0.518665987302818</v>
       </c>
       <c r="I66" t="n">
         <v>10.98945806195804</v>
       </c>
       <c r="J66" t="n">
-        <v>1.584932552414528</v>
+        <v>0.6130698752332027</v>
       </c>
       <c r="K66" t="n">
         <v>10.98945806195804</v>
@@ -3107,13 +3107,13 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4377945024002811</v>
+        <v>10.98945806195804</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.4377945024002811</v>
+        <v>10.98945806195804</v>
       </c>
     </row>
     <row r="73">
@@ -3144,13 +3144,13 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0.7499070502279765</v>
+        <v>10.98945806195804</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0.7499070502279765</v>
+        <v>10.98945806195804</v>
       </c>
     </row>
     <row r="74">
@@ -3181,13 +3181,13 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>0.9961630151776049</v>
+        <v>10.98945806195804</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0.9961630151776049</v>
+        <v>10.98945806195804</v>
       </c>
     </row>
     <row r="75">
@@ -3218,13 +3218,13 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>1.200860529458417</v>
+        <v>10.98945806195804</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>1.200860529458417</v>
+        <v>10.98945806195804</v>
       </c>
     </row>
     <row r="76">
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>1.376405547724845</v>
+        <v>10.98945806195804</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>1.376405547724845</v>
+        <v>10.98945806195804</v>
       </c>
     </row>
     <row r="77">
@@ -3292,13 +3292,13 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4377945024002811</v>
+        <v>10.98945806195804</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0.4377945024002811</v>
+        <v>10.98945806195804</v>
       </c>
     </row>
     <row r="78">
@@ -3329,13 +3329,13 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>0.7499070502279765</v>
+        <v>10.98945806195804</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0.7499070502279765</v>
+        <v>10.98945806195804</v>
       </c>
     </row>
     <row r="79">
@@ -3366,13 +3366,13 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>0.9961630151776049</v>
+        <v>10.98945806195804</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0.9961630151776049</v>
+        <v>10.98945806195804</v>
       </c>
     </row>
     <row r="80">
@@ -3403,13 +3403,13 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>1.200860529458417</v>
+        <v>10.98945806195804</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>1.200860529458417</v>
+        <v>10.98945806195804</v>
       </c>
     </row>
     <row r="81">
@@ -3440,13 +3440,13 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>1.376405547724845</v>
+        <v>10.98945806195804</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>1.376405547724845</v>
+        <v>10.98945806195804</v>
       </c>
     </row>
     <row r="82">
